--- a/data/trans_orig/P6603-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6603-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2007</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228436</t>
+          <t>226113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>266315</t>
+          <t>265039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114576</t>
+          <t>115607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134379</t>
+          <t>134686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>352817</t>
+          <t>352272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>394468</t>
+          <t>395513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>65185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96299</t>
+          <t>98920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84518</t>
+          <t>83749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122354</t>
+          <t>119248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39016</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66237</t>
+          <t>65838</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43917</t>
+          <t>44311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74786</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>352158</t>
+          <t>354154</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399504</t>
+          <t>400060</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>211464</t>
+          <t>210300</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236208</t>
+          <t>235846</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>576151</t>
+          <t>574224</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>630026</t>
+          <t>629491</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78806</t>
+          <t>78982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115661</t>
+          <t>116764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102392</t>
+          <t>101204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145578</t>
+          <t>145615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43434</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73371</t>
+          <t>71536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54726</t>
+          <t>55879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>44558</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263123</t>
+          <t>262724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302152</t>
+          <t>300783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181435</t>
+          <t>181291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199798</t>
+          <t>199773</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>455384</t>
+          <t>452247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>497832</t>
+          <t>495753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55823</t>
+          <t>55620</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86581</t>
+          <t>86035</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69114</t>
+          <t>68848</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103972</t>
+          <t>103834</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>28985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54153</t>
+          <t>53569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29903</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>367913</t>
+          <t>363894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>410595</t>
+          <t>408238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307028</t>
+          <t>307249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>339050</t>
+          <t>338270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>685960</t>
+          <t>686889</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>739499</t>
+          <t>738401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57927</t>
+          <t>57063</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90583</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25041</t>
+          <t>25547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>47764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87118</t>
+          <t>91063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126679</t>
+          <t>128331</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48749</t>
+          <t>51403</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78578</t>
+          <t>80585</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>32353</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>68028</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104723</t>
+          <t>103647</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>39926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>48803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1259391</t>
+          <t>1259209</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1341737</t>
+          <t>1345563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>840703</t>
+          <t>845076</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>889758</t>
+          <t>890475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2115606</t>
+          <t>2111577</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2211721</t>
+          <t>2212091</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>288570</t>
+          <t>282871</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>353136</t>
+          <t>350272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80854</t>
+          <t>80696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119561</t>
+          <t>118340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>376381</t>
+          <t>379699</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>458903</t>
+          <t>460043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>181791</t>
+          <t>182402</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>233660</t>
+          <t>236134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>32025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59395</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>225083</t>
+          <t>222327</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>286413</t>
+          <t>285307</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>61985</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99006</t>
+          <t>97923</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>73576</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>111363</t>
+          <t>112267</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2012</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121456</t>
+          <t>118693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154797</t>
+          <t>155241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117122</t>
+          <t>117807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138989</t>
+          <t>138398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246557</t>
+          <t>248160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>287840</t>
+          <t>288061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47899</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75752</t>
+          <t>77499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65796</t>
+          <t>66197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97647</t>
+          <t>97917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41688</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71308</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36208</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>36858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>209753</t>
+          <t>211811</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>252469</t>
+          <t>254507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>194044</t>
+          <t>195493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>222767</t>
+          <t>223542</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>416185</t>
+          <t>413291</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>469003</t>
+          <t>466092</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80678</t>
+          <t>81647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117050</t>
+          <t>116764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>26983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52552</t>
+          <t>50635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114290</t>
+          <t>114895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159034</t>
+          <t>160920</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63344</t>
+          <t>62848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>46939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76733</t>
+          <t>78625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44944</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17192</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>57472</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170121</t>
+          <t>169740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208738</t>
+          <t>207458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153260</t>
+          <t>155605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180809</t>
+          <t>180418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>334098</t>
+          <t>333170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377562</t>
+          <t>380593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56571</t>
+          <t>58944</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88501</t>
+          <t>90686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39696</t>
+          <t>38246</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>81312</t>
+          <t>82386</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>121295</t>
+          <t>120802</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57204</t>
+          <t>58169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,47 +5224,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>55299</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>42228</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>72300</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>10,36%</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>55299</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>40940</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>72926</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27436</t>
+          <t>25417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>33095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>239911</t>
+          <t>238981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>278845</t>
+          <t>278036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>214187</t>
+          <t>212006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244108</t>
+          <t>244021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>461906</t>
+          <t>462554</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>512857</t>
+          <t>510820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81140</t>
+          <t>79326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>115877</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>33983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>59499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122111</t>
+          <t>121222</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165160</t>
+          <t>165105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47805</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21082</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34277</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>62874</t>
+          <t>61200</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39376</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>25168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31572</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57555</t>
+          <t>57016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>779341</t>
+          <t>779188</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>856005</t>
+          <t>857095</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>707936</t>
+          <t>708492</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>762685</t>
+          <t>761548</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1510403</t>
+          <t>1507061</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1606919</t>
+          <t>1601993</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>297062</t>
+          <t>297431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>363959</t>
+          <t>367284</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109881</t>
+          <t>108099</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154221</t>
+          <t>152475</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>419628</t>
+          <t>415562</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>497480</t>
+          <t>498463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143943</t>
+          <t>145710</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>192969</t>
+          <t>194236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>37785</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66028</t>
+          <t>66421</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>187604</t>
+          <t>187486</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247294</t>
+          <t>247504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>81345</t>
+          <t>78666</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123982</t>
+          <t>120281</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>43780</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>107443</t>
+          <t>104160</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>155538</t>
+          <t>152538</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2016</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125393</t>
+          <t>125586</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156378</t>
+          <t>157151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115796</t>
+          <t>116303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137320</t>
+          <t>138669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248898</t>
+          <t>248611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>286711</t>
+          <t>285684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42211</t>
+          <t>42554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69448</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37786</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>67316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99264</t>
+          <t>101249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25568</t>
+          <t>25166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>48613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33698</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>58840</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>20227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22793</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213013</t>
+          <t>213263</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254094</t>
+          <t>254673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>191136</t>
+          <t>191449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220906</t>
+          <t>220079</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>413242</t>
+          <t>415593</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>464999</t>
+          <t>463987</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93027</t>
+          <t>93665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130144</t>
+          <t>130376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54973</t>
+          <t>54902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132277</t>
+          <t>130444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176742</t>
+          <t>174883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69348</t>
+          <t>71706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>28489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>57042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90397</t>
+          <t>89645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143989</t>
+          <t>143305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183101</t>
+          <t>185155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168207</t>
+          <t>167842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199271</t>
+          <t>199310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322753</t>
+          <t>323376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374425</t>
+          <t>374631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104048</t>
+          <t>103954</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>140439</t>
+          <t>141525</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42132</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67316</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>151849</t>
+          <t>152117</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>198585</t>
+          <t>195628</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>44666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74807</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66743</t>
+          <t>67559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101783</t>
+          <t>102554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28372</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18135</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>245548</t>
+          <t>245603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>283617</t>
+          <t>283668</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250974</t>
+          <t>252965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280766</t>
+          <t>280453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>506790</t>
+          <t>507076</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>556673</t>
+          <t>555014</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62624</t>
+          <t>63145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93275</t>
+          <t>93464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28739</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53510</t>
+          <t>51926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98282</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137650</t>
+          <t>136442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52672</t>
+          <t>52608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37329</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64597</t>
+          <t>65027</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>27562</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>764918</t>
+          <t>759418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>839964</t>
+          <t>840885</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>757089</t>
+          <t>759507</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>812594</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1538775</t>
+          <t>1540366</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1632784</t>
+          <t>1632782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>329606</t>
+          <t>329480</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>394635</t>
+          <t>400574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141496</t>
+          <t>140067</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>187178</t>
+          <t>185014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>488792</t>
+          <t>485267</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>568057</t>
+          <t>567448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>164993</t>
+          <t>163514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>215797</t>
+          <t>215436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79408</t>
+          <t>79526</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>220571</t>
+          <t>221468</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282125</t>
+          <t>283354</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>74330</t>
+          <t>75377</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>15832</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>37021</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>64546</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>102366</t>
+          <t>101648</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2023</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65756</t>
+          <t>66722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97097</t>
+          <t>96933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81703</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98881</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155332</t>
+          <t>153063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190579</t>
+          <t>189219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,81%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53527</t>
+          <t>54450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>84189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>33809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78753</t>
+          <t>78838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112277</t>
+          <t>114516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>27208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>290154</t>
+          <t>288679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>500152</t>
+          <t>496739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112403</t>
+          <t>112658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135063</t>
+          <t>136957</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>420081</t>
+          <t>418153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>654042</t>
+          <t>648305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167767</t>
+          <t>170703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44903</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66383</t>
+          <t>67279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56288</t>
+          <t>58682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222358</t>
+          <t>223492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64474</t>
+          <t>67934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19474</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73016</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>27378</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92953</t>
+          <t>93156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121692</t>
+          <t>121620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116756</t>
+          <t>116711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146122</t>
+          <t>148796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217871</t>
+          <t>217325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269622</t>
+          <t>267744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34407</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>61430</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>48983</t>
+          <t>49342</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91463</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>27698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>155171</t>
+          <t>155074</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>182565</t>
+          <t>182195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>142214</t>
+          <t>141645</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159988</t>
+          <t>159698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>303446</t>
+          <t>303062</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337816</t>
+          <t>337415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>47085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30531</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44621</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72147</t>
+          <t>72032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>26463</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32284</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24185</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>657515</t>
+          <t>661103</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>937412</t>
+          <t>920563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>477023</t>
+          <t>472737</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>529055</t>
+          <t>527102</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1170891</t>
+          <t>1164317</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1445781</t>
+          <t>1456615</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120781</t>
+          <t>132581</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>318474</t>
+          <t>315340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105481</t>
+          <t>106739</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148772</t>
+          <t>150833</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246938</t>
+          <t>234111</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>438387</t>
+          <t>441833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36328</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107647</t>
+          <t>108044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64923</t>
+          <t>69599</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129166</t>
+          <t>133115</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>44938</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>31018</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>71456</t>
+          <t>74093</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6603-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6603-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226113</t>
+          <t>226593</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>265039</t>
+          <t>264796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115607</t>
+          <t>115674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134686</t>
+          <t>134930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>352272</t>
+          <t>350985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>395513</t>
+          <t>393555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65185</t>
+          <t>64843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98920</t>
+          <t>96583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83749</t>
+          <t>84005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119248</t>
+          <t>118764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38001</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65838</t>
+          <t>66757</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>44082</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>74790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>354154</t>
+          <t>354240</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>400060</t>
+          <t>400537</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210300</t>
+          <t>211397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>235846</t>
+          <t>235956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>574224</t>
+          <t>575285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>629491</t>
+          <t>630679</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78982</t>
+          <t>77529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116764</t>
+          <t>114795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36929</t>
+          <t>36952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101204</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145615</t>
+          <t>144384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71536</t>
+          <t>72261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23566</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55879</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87887</t>
+          <t>88232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262724</t>
+          <t>263070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300783</t>
+          <t>301900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181291</t>
+          <t>181868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199773</t>
+          <t>199690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>452247</t>
+          <t>454023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>495753</t>
+          <t>497478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55620</t>
+          <t>55503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86035</t>
+          <t>87288</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>68848</t>
+          <t>70567</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103834</t>
+          <t>107255</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>51899</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28985</t>
+          <t>27715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53569</t>
+          <t>53857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>26057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>30464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>363894</t>
+          <t>368263</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>408238</t>
+          <t>410800</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307249</t>
+          <t>307866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>338270</t>
+          <t>337550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>686889</t>
+          <t>687784</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>738401</t>
+          <t>739569</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57063</t>
+          <t>58722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>91736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47764</t>
+          <t>47684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91063</t>
+          <t>89676</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128331</t>
+          <t>129108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>50823</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80585</t>
+          <t>78892</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>32968</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>68771</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103647</t>
+          <t>103636</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24470</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>47856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1259209</t>
+          <t>1255656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1345563</t>
+          <t>1337941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845076</t>
+          <t>842658</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>890475</t>
+          <t>889304</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2111577</t>
+          <t>2118440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2212091</t>
+          <t>2214302</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>282871</t>
+          <t>288368</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>350272</t>
+          <t>354268</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80696</t>
+          <t>81518</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118340</t>
+          <t>119157</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>379699</t>
+          <t>381825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>460043</t>
+          <t>458727</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>182402</t>
+          <t>182482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>236134</t>
+          <t>238683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>59005</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222327</t>
+          <t>222824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285307</t>
+          <t>286625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>97923</t>
+          <t>97534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>73576</t>
+          <t>73378</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>112267</t>
+          <t>112961</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118693</t>
+          <t>120313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155241</t>
+          <t>154394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117807</t>
+          <t>118555</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138398</t>
+          <t>138875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248160</t>
+          <t>245411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>288061</t>
+          <t>286384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47976</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77499</t>
+          <t>75444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66197</t>
+          <t>65109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97917</t>
+          <t>96423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31443</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56830</t>
+          <t>56193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70344</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36858</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211811</t>
+          <t>211111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254507</t>
+          <t>253089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>195493</t>
+          <t>194506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>223542</t>
+          <t>221645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>413291</t>
+          <t>413027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>466092</t>
+          <t>468205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116764</t>
+          <t>118424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26983</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>51752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114895</t>
+          <t>115803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160920</t>
+          <t>160290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36815</t>
+          <t>35081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62848</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>46457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78625</t>
+          <t>76744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45603</t>
+          <t>44674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57472</t>
+          <t>55542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169740</t>
+          <t>168468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207458</t>
+          <t>206177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155605</t>
+          <t>154000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180418</t>
+          <t>181237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333170</t>
+          <t>333594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380593</t>
+          <t>379389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58944</t>
+          <t>58383</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90686</t>
+          <t>89707</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>39978</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82386</t>
+          <t>82612</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120802</t>
+          <t>118932</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58169</t>
+          <t>57029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42228</t>
+          <t>41181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72300</t>
+          <t>73656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>32268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238981</t>
+          <t>236666</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>278036</t>
+          <t>277915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>212006</t>
+          <t>213691</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244021</t>
+          <t>244540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>462554</t>
+          <t>459608</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>510820</t>
+          <t>512418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79326</t>
+          <t>79929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115877</t>
+          <t>115052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>34171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59499</t>
+          <t>59411</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121222</t>
+          <t>121546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165105</t>
+          <t>165618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46999</t>
+          <t>47534</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21028</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>34448</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61200</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>57790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>779188</t>
+          <t>776032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>857095</t>
+          <t>860781</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>708492</t>
+          <t>709345</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>761548</t>
+          <t>763073</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1507061</t>
+          <t>1506696</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1601993</t>
+          <t>1603607</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>297431</t>
+          <t>293191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>367284</t>
+          <t>362185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108099</t>
+          <t>107677</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152475</t>
+          <t>153214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>415562</t>
+          <t>421771</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>498463</t>
+          <t>503318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145710</t>
+          <t>143759</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>194236</t>
+          <t>193783</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66421</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>187486</t>
+          <t>188918</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247504</t>
+          <t>247523</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>81369</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>120281</t>
+          <t>123239</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>43780</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>107322</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>152538</t>
+          <t>152730</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125586</t>
+          <t>125424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157151</t>
+          <t>156045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116303</t>
+          <t>117386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138669</t>
+          <t>137392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248611</t>
+          <t>249570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285684</t>
+          <t>286621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42554</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69059</t>
+          <t>69281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18644</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67316</t>
+          <t>66212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101249</t>
+          <t>99967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48613</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34211</t>
+          <t>34573</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58840</t>
+          <t>59249</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213263</t>
+          <t>211063</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254673</t>
+          <t>252817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>191449</t>
+          <t>190637</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220079</t>
+          <t>220233</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>415593</t>
+          <t>413130</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>463987</t>
+          <t>464136</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93665</t>
+          <t>93080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130376</t>
+          <t>130283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31877</t>
+          <t>31259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54902</t>
+          <t>55039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130444</t>
+          <t>130978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174883</t>
+          <t>175329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41712</t>
+          <t>41937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71706</t>
+          <t>67518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57042</t>
+          <t>57682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89645</t>
+          <t>91555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143305</t>
+          <t>141813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185155</t>
+          <t>182984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167842</t>
+          <t>169517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199310</t>
+          <t>200097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323376</t>
+          <t>320859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374631</t>
+          <t>373890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103954</t>
+          <t>103485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141525</t>
+          <t>141357</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67241</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>152117</t>
+          <t>152793</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>195628</t>
+          <t>196635</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44666</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74575</t>
+          <t>73354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>35054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67559</t>
+          <t>66420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102554</t>
+          <t>102498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>28097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>245603</t>
+          <t>245437</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>283668</t>
+          <t>283081</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252965</t>
+          <t>253194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280453</t>
+          <t>280249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>507076</t>
+          <t>506533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>555014</t>
+          <t>557113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63145</t>
+          <t>62015</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93464</t>
+          <t>94998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>51628</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96142</t>
+          <t>97949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136442</t>
+          <t>138618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28757</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52608</t>
+          <t>53035</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>37039</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>66369</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27562</t>
+          <t>28258</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>759418</t>
+          <t>764014</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>840885</t>
+          <t>839588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>759507</t>
+          <t>761002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>813243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1540366</t>
+          <t>1541875</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1632782</t>
+          <t>1632609</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>329480</t>
+          <t>331582</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>400574</t>
+          <t>403969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140067</t>
+          <t>139453</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>185014</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>485267</t>
+          <t>487741</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>567448</t>
+          <t>567341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>163514</t>
+          <t>163881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>215436</t>
+          <t>215051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47871</t>
+          <t>48217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79526</t>
+          <t>79007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>221468</t>
+          <t>219772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>283354</t>
+          <t>283208</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>75377</t>
+          <t>75769</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>37021</t>
+          <t>35381</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>66488</t>
+          <t>66217</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>101648</t>
+          <t>102727</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>81492</t>
+          <t>96604</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66722</t>
+          <t>80204</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96933</t>
+          <t>112918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>91341</t>
+          <t>99656</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83019</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98977</t>
+          <t>107910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>172833</t>
+          <t>196259</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153063</t>
+          <t>177290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189219</t>
+          <t>215588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>71840</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54450</t>
+          <t>57296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84189</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25980</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>94334</t>
+          <t>101952</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78838</t>
+          <t>85615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114516</t>
+          <t>119654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31324</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,22 +10333,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,22 +10368,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>408591</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>288679</t>
+          <t>159246</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>496739</t>
+          <t>199822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>124303</t>
+          <t>136276</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112658</t>
+          <t>122956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136957</t>
+          <t>148647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>532892</t>
+          <t>316276</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>418153</t>
+          <t>291628</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>648305</t>
+          <t>339641</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88353</t>
+          <t>103026</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>84309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170703</t>
+          <t>121965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54767</t>
+          <t>58855</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44752</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67279</t>
+          <t>71405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>143121</t>
+          <t>161880</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58682</t>
+          <t>141340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223492</t>
+          <t>184335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67934</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>44605</t>
+          <t>48659</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74848</t>
+          <t>66052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>24464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>37449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>540811</t>
+          <t>331486</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>540811</t>
+          <t>331486</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>540811</t>
+          <t>331486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>200728</t>
+          <t>218951</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200728</t>
+          <t>218951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200728</t>
+          <t>218951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>741538</t>
+          <t>550436</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>741538</t>
+          <t>550436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>741538</t>
+          <t>550436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>107978</t>
+          <t>117429</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93156</t>
+          <t>100117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121620</t>
+          <t>133168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>130226</t>
+          <t>115566</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116711</t>
+          <t>104952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148796</t>
+          <t>124844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>238204</t>
+          <t>232995</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>213237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267744</t>
+          <t>253625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46041</t>
+          <t>54524</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>41256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61430</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>29096</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>72764</t>
+          <t>83620</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>49342</t>
+          <t>67160</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91850</t>
+          <t>100922</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>43504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>30688</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27698</t>
+          <t>49950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>169874</t>
+          <t>185446</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>155074</t>
+          <t>170657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>182195</t>
+          <t>199650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>151245</t>
+          <t>164471</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141645</t>
+          <t>152926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159698</t>
+          <t>174029</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>321119</t>
+          <t>349916</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>303062</t>
+          <t>330192</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337415</t>
+          <t>367493</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,45%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>34718</t>
+          <t>38942</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>28775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>34597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>65142</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72032</t>
+          <t>81510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26463</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>36933</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>13406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>28075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>767934</t>
+          <t>579479</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>661103</t>
+          <t>545426</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>920563</t>
+          <t>612146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>497114</t>
+          <t>515968</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>472737</t>
+          <t>494706</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>527102</t>
+          <t>537979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1265049</t>
+          <t>1095447</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1164317</t>
+          <t>1051237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1456615</t>
+          <t>1135471</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>237467</t>
+          <t>268331</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132581</t>
+          <t>239444</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>315340</t>
+          <t>297611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>129569</t>
+          <t>144263</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>126743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150833</t>
+          <t>164275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>367036</t>
+          <t>412595</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>234111</t>
+          <t>379292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>441833</t>
+          <t>447997</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>77418</t>
+          <t>97031</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>76842</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108044</t>
+          <t>121804</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>125322</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69599</t>
+          <t>103127</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133115</t>
+          <t>153716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44938</t>
+          <t>47540</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>54358</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>47148</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>74093</t>
+          <t>82761</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1111204</t>
+          <t>976451</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1111204</t>
+          <t>976451</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1111204</t>
+          <t>976451</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>678048</t>
+          <t>718652</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>678048</t>
+          <t>718652</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>678048</t>
+          <t>718652</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1789252</t>
+          <t>1695103</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1789252</t>
+          <t>1695103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1789252</t>
+          <t>1695103</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
